--- a/doc/公司名单.xlsx
+++ b/doc/公司名单.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Samsung_SSD_990_PRO_2TB_Media/life_os/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCBFFF53-66FC-0C4B-8CBA-5AEF49BB6EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D837F53B-DFD4-0D43-A73B-5AA6CE87B070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4320" yWindow="1080" windowWidth="24480" windowHeight="15900" xr2:uid="{4A6C4FA4-6154-7C4A-8AB0-8DCB44C7ED28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -314,9 +314,6 @@
     <t>自身免疫/抗体药</t>
   </si>
   <si>
-    <t>荣昌生物</t>
-  </si>
-  <si>
     <t>烟台/上海</t>
   </si>
   <si>
@@ -698,6 +695,10 @@
   </si>
   <si>
     <t>康诺亚（Keymed）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>荣昌生物</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -722,7 +723,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -732,6 +733,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -750,11 +757,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1276,31 +1286,31 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5" t="s">
         <v>188</v>
-      </c>
-      <c r="E5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5" t="s">
-        <v>189</v>
       </c>
       <c r="M5" t="s">
         <v>33</v>
@@ -1320,7 +1330,7 @@
         <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -1390,7 +1400,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -1443,7 +1453,7 @@
         <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -1472,7 +1482,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1484,7 +1494,7 @@
         <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -1513,7 +1523,7 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1525,7 +1535,7 @@
         <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -1636,7 +1646,7 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1758,8 +1768,8 @@
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>212</v>
+      <c r="A17" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="B17" t="s">
         <v>54</v>
@@ -1799,8 +1809,8 @@
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" t="s">
-        <v>213</v>
+      <c r="A18" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="B18" t="s">
         <v>54</v>
@@ -1840,7 +1850,7 @@
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B19" t="s">
@@ -1881,7 +1891,7 @@
       </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" t="s">
+      <c r="A20" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B20" t="s">
@@ -1894,7 +1904,7 @@
         <v>64</v>
       </c>
       <c r="E20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -1922,7 +1932,7 @@
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" t="s">
+      <c r="A21" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B21" t="s">
@@ -1963,7 +1973,7 @@
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B22" t="s">
@@ -2004,7 +2014,7 @@
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" t="s">
+      <c r="A23" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B23" t="s">
@@ -2045,7 +2055,7 @@
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" t="s">
+      <c r="A24" s="2" t="s">
         <v>75</v>
       </c>
       <c r="B24" t="s">
@@ -2085,11 +2095,11 @@
         <v>20</v>
       </c>
       <c r="N24" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" t="s">
+      <c r="A25" s="2" t="s">
         <v>79</v>
       </c>
       <c r="B25" t="s">
@@ -2130,7 +2140,7 @@
       </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" t="s">
+      <c r="A26" s="2" t="s">
         <v>82</v>
       </c>
       <c r="B26" t="s">
@@ -2171,7 +2181,7 @@
       </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" t="s">
+      <c r="A27" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B27" t="s">
@@ -2212,8 +2222,8 @@
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" t="s">
-        <v>217</v>
+      <c r="A28" s="2" t="s">
+        <v>216</v>
       </c>
       <c r="B28" t="s">
         <v>54</v>
@@ -2254,13 +2264,13 @@
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>217</v>
       </c>
       <c r="B29" t="s">
         <v>54</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s">
         <v>91</v>
@@ -2295,7 +2305,7 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B30" t="s">
         <v>54</v>
@@ -2304,10 +2314,10 @@
         <v>76</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
@@ -2328,7 +2338,7 @@
         <v>4</v>
       </c>
       <c r="L30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M30" t="s">
         <v>45</v>
@@ -2336,7 +2346,7 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B31" t="s">
         <v>54</v>
@@ -2345,7 +2355,7 @@
         <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E31" t="s">
         <v>58</v>
@@ -2377,16 +2387,16 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B32" t="s">
         <v>54</v>
       </c>
       <c r="C32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" t="s">
         <v>99</v>
-      </c>
-      <c r="D32" t="s">
-        <v>100</v>
       </c>
       <c r="E32" t="s">
         <v>17</v>
@@ -2410,7 +2420,7 @@
         <v>4</v>
       </c>
       <c r="L32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M32" t="s">
         <v>45</v>
@@ -2418,7 +2428,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
         <v>54</v>
@@ -2427,7 +2437,7 @@
         <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E33" t="s">
         <v>23</v>
@@ -2459,7 +2469,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B34" t="s">
         <v>54</v>
@@ -2468,31 +2478,31 @@
         <v>15</v>
       </c>
       <c r="D34" t="s">
+        <v>104</v>
+      </c>
+      <c r="E34" t="s">
         <v>105</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34">
+        <v>4</v>
+      </c>
+      <c r="H34">
+        <v>4</v>
+      </c>
+      <c r="I34">
+        <v>3</v>
+      </c>
+      <c r="J34">
+        <v>5</v>
+      </c>
+      <c r="K34">
+        <v>4</v>
+      </c>
+      <c r="L34" t="s">
         <v>106</v>
-      </c>
-      <c r="F34" t="s">
-        <v>18</v>
-      </c>
-      <c r="G34">
-        <v>4</v>
-      </c>
-      <c r="H34">
-        <v>4</v>
-      </c>
-      <c r="I34">
-        <v>3</v>
-      </c>
-      <c r="J34">
-        <v>5</v>
-      </c>
-      <c r="K34">
-        <v>4</v>
-      </c>
-      <c r="L34" t="s">
-        <v>107</v>
       </c>
       <c r="M34" t="s">
         <v>33</v>
@@ -2500,7 +2510,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s">
         <v>54</v>
@@ -2509,7 +2519,7 @@
         <v>76</v>
       </c>
       <c r="D35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E35" t="s">
         <v>23</v>
@@ -2533,7 +2543,7 @@
         <v>4</v>
       </c>
       <c r="L35" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M35" t="s">
         <v>48</v>
@@ -2541,16 +2551,16 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B36" t="s">
         <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D36" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E36" t="s">
         <v>17</v>
@@ -2574,7 +2584,7 @@
         <v>4</v>
       </c>
       <c r="L36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M36" t="s">
         <v>33</v>
@@ -2582,7 +2592,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B37" t="s">
         <v>54</v>
@@ -2591,10 +2601,10 @@
         <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
@@ -2623,7 +2633,7 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B38" t="s">
         <v>54</v>
@@ -2632,31 +2642,31 @@
         <v>15</v>
       </c>
       <c r="D38" t="s">
+        <v>194</v>
+      </c>
+      <c r="E38" t="s">
+        <v>192</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38">
+        <v>3</v>
+      </c>
+      <c r="H38">
+        <v>4</v>
+      </c>
+      <c r="I38">
+        <v>3</v>
+      </c>
+      <c r="J38">
+        <v>4</v>
+      </c>
+      <c r="K38">
+        <v>4</v>
+      </c>
+      <c r="L38" t="s">
         <v>195</v>
-      </c>
-      <c r="E38" t="s">
-        <v>193</v>
-      </c>
-      <c r="F38" t="s">
-        <v>18</v>
-      </c>
-      <c r="G38">
-        <v>3</v>
-      </c>
-      <c r="H38">
-        <v>4</v>
-      </c>
-      <c r="I38">
-        <v>3</v>
-      </c>
-      <c r="J38">
-        <v>4</v>
-      </c>
-      <c r="K38">
-        <v>4</v>
-      </c>
-      <c r="L38" t="s">
-        <v>196</v>
       </c>
       <c r="M38" t="s">
         <v>48</v>
@@ -2664,40 +2674,40 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B39" t="s">
         <v>54</v>
       </c>
       <c r="C39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D39" t="s">
+        <v>197</v>
+      </c>
+      <c r="E39" t="s">
+        <v>192</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39">
+        <v>5</v>
+      </c>
+      <c r="H39">
+        <v>4</v>
+      </c>
+      <c r="I39">
+        <v>3</v>
+      </c>
+      <c r="J39">
+        <v>5</v>
+      </c>
+      <c r="K39">
+        <v>4</v>
+      </c>
+      <c r="L39" t="s">
         <v>198</v>
-      </c>
-      <c r="E39" t="s">
-        <v>193</v>
-      </c>
-      <c r="F39" t="s">
-        <v>18</v>
-      </c>
-      <c r="G39">
-        <v>5</v>
-      </c>
-      <c r="H39">
-        <v>4</v>
-      </c>
-      <c r="I39">
-        <v>3</v>
-      </c>
-      <c r="J39">
-        <v>5</v>
-      </c>
-      <c r="K39">
-        <v>4</v>
-      </c>
-      <c r="L39" t="s">
-        <v>199</v>
       </c>
       <c r="M39" t="s">
         <v>20</v>
@@ -2705,13 +2715,13 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B40" t="s">
         <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D40" t="s">
         <v>61</v>
@@ -2738,7 +2748,7 @@
         <v>3</v>
       </c>
       <c r="L40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M40" t="s">
         <v>48</v>
@@ -2746,19 +2756,19 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B41" t="s">
         <v>54</v>
       </c>
       <c r="C41" t="s">
+        <v>118</v>
+      </c>
+      <c r="D41" t="s">
         <v>119</v>
       </c>
-      <c r="D41" t="s">
-        <v>120</v>
-      </c>
       <c r="E41" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F41" t="s">
         <v>18</v>
@@ -2787,16 +2797,16 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B42" t="s">
         <v>54</v>
       </c>
       <c r="C42" t="s">
+        <v>121</v>
+      </c>
+      <c r="D42" t="s">
         <v>122</v>
-      </c>
-      <c r="D42" t="s">
-        <v>123</v>
       </c>
       <c r="E42" t="s">
         <v>17</v>
@@ -2820,7 +2830,7 @@
         <v>4</v>
       </c>
       <c r="L42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M42" t="s">
         <v>48</v>
@@ -2828,13 +2838,13 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B43" t="s">
         <v>54</v>
       </c>
       <c r="C43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D43" t="s">
         <v>61</v>
@@ -2861,7 +2871,7 @@
         <v>3</v>
       </c>
       <c r="L43" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M43" t="s">
         <v>48</v>
@@ -2869,7 +2879,7 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B44" t="s">
         <v>54</v>
@@ -2878,7 +2888,7 @@
         <v>15</v>
       </c>
       <c r="D44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E44" t="s">
         <v>23</v>
@@ -2910,19 +2920,19 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45" t="s">
         <v>128</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>129</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>130</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>131</v>
-      </c>
-      <c r="E45" t="s">
-        <v>132</v>
       </c>
       <c r="F45" t="s">
         <v>18</v>
@@ -2943,27 +2953,27 @@
         <v>2</v>
       </c>
       <c r="L45" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M45" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" t="s">
+        <v>133</v>
+      </c>
+      <c r="B46" t="s">
         <v>134</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
+        <v>98</v>
+      </c>
+      <c r="D46" t="s">
         <v>135</v>
       </c>
-      <c r="C46" t="s">
-        <v>99</v>
-      </c>
-      <c r="D46" t="s">
-        <v>136</v>
-      </c>
       <c r="E46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F46" t="s">
         <v>18</v>
@@ -2984,48 +2994,48 @@
         <v>2</v>
       </c>
       <c r="L46" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M46" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" t="s">
+        <v>137</v>
+      </c>
+      <c r="B47" t="s">
         <v>138</v>
-      </c>
-      <c r="B47" t="s">
-        <v>139</v>
       </c>
       <c r="C47" t="s">
         <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E47" t="s">
+        <v>199</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47">
+        <v>5</v>
+      </c>
+      <c r="H47">
+        <v>5</v>
+      </c>
+      <c r="I47">
+        <v>4</v>
+      </c>
+      <c r="J47">
+        <v>5</v>
+      </c>
+      <c r="K47">
+        <v>4</v>
+      </c>
+      <c r="L47" t="s">
         <v>200</v>
-      </c>
-      <c r="F47" t="s">
-        <v>18</v>
-      </c>
-      <c r="G47">
-        <v>5</v>
-      </c>
-      <c r="H47">
-        <v>5</v>
-      </c>
-      <c r="I47">
-        <v>4</v>
-      </c>
-      <c r="J47">
-        <v>5</v>
-      </c>
-      <c r="K47">
-        <v>4</v>
-      </c>
-      <c r="L47" t="s">
-        <v>201</v>
       </c>
       <c r="M47" t="s">
         <v>20</v>
@@ -3033,19 +3043,19 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C48" t="s">
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E48" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F48" t="s">
         <v>18</v>
@@ -3066,7 +3076,7 @@
         <v>4</v>
       </c>
       <c r="L48" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M48" t="s">
         <v>20</v>
@@ -3074,19 +3084,19 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C49" t="s">
         <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E49" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F49" t="s">
         <v>18</v>
@@ -3107,7 +3117,7 @@
         <v>4</v>
       </c>
       <c r="L49" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M49" t="s">
         <v>20</v>
@@ -3115,40 +3125,40 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C50" t="s">
         <v>15</v>
       </c>
       <c r="D50" t="s">
+        <v>145</v>
+      </c>
+      <c r="E50" t="s">
         <v>146</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50">
+        <v>5</v>
+      </c>
+      <c r="H50">
+        <v>4</v>
+      </c>
+      <c r="I50">
+        <v>4</v>
+      </c>
+      <c r="J50">
+        <v>4</v>
+      </c>
+      <c r="K50">
+        <v>4</v>
+      </c>
+      <c r="L50" t="s">
         <v>147</v>
-      </c>
-      <c r="F50" t="s">
-        <v>18</v>
-      </c>
-      <c r="G50">
-        <v>5</v>
-      </c>
-      <c r="H50">
-        <v>4</v>
-      </c>
-      <c r="I50">
-        <v>4</v>
-      </c>
-      <c r="J50">
-        <v>4</v>
-      </c>
-      <c r="K50">
-        <v>4</v>
-      </c>
-      <c r="L50" t="s">
-        <v>148</v>
       </c>
       <c r="M50" t="s">
         <v>20</v>
@@ -3156,40 +3166,40 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B51" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C51" t="s">
         <v>15</v>
       </c>
       <c r="D51" t="s">
+        <v>149</v>
+      </c>
+      <c r="E51" t="s">
+        <v>146</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51">
+        <v>5</v>
+      </c>
+      <c r="H51">
+        <v>5</v>
+      </c>
+      <c r="I51">
+        <v>4</v>
+      </c>
+      <c r="J51">
+        <v>4</v>
+      </c>
+      <c r="K51">
+        <v>4</v>
+      </c>
+      <c r="L51" t="s">
         <v>150</v>
-      </c>
-      <c r="E51" t="s">
-        <v>147</v>
-      </c>
-      <c r="F51" t="s">
-        <v>18</v>
-      </c>
-      <c r="G51">
-        <v>5</v>
-      </c>
-      <c r="H51">
-        <v>5</v>
-      </c>
-      <c r="I51">
-        <v>4</v>
-      </c>
-      <c r="J51">
-        <v>4</v>
-      </c>
-      <c r="K51">
-        <v>4</v>
-      </c>
-      <c r="L51" t="s">
-        <v>151</v>
       </c>
       <c r="M51" t="s">
         <v>20</v>
@@ -3197,40 +3207,40 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B52" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C52" t="s">
         <v>15</v>
       </c>
       <c r="D52" t="s">
+        <v>152</v>
+      </c>
+      <c r="E52" t="s">
+        <v>146</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52">
+        <v>4</v>
+      </c>
+      <c r="H52">
+        <v>5</v>
+      </c>
+      <c r="I52">
+        <v>4</v>
+      </c>
+      <c r="J52">
+        <v>4</v>
+      </c>
+      <c r="K52">
+        <v>4</v>
+      </c>
+      <c r="L52" t="s">
         <v>153</v>
-      </c>
-      <c r="E52" t="s">
-        <v>147</v>
-      </c>
-      <c r="F52" t="s">
-        <v>18</v>
-      </c>
-      <c r="G52">
-        <v>4</v>
-      </c>
-      <c r="H52">
-        <v>5</v>
-      </c>
-      <c r="I52">
-        <v>4</v>
-      </c>
-      <c r="J52">
-        <v>4</v>
-      </c>
-      <c r="K52">
-        <v>4</v>
-      </c>
-      <c r="L52" t="s">
-        <v>154</v>
       </c>
       <c r="M52" t="s">
         <v>33</v>
@@ -3238,19 +3248,19 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B53" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C53" t="s">
         <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E53" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F53" t="s">
         <v>18</v>
@@ -3271,7 +3281,7 @@
         <v>4</v>
       </c>
       <c r="L53" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M53" t="s">
         <v>33</v>
@@ -3279,40 +3289,40 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B54" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C54" t="s">
         <v>15</v>
       </c>
       <c r="D54" t="s">
+        <v>157</v>
+      </c>
+      <c r="E54" t="s">
+        <v>146</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54">
+        <v>4</v>
+      </c>
+      <c r="H54">
+        <v>4</v>
+      </c>
+      <c r="I54">
+        <v>4</v>
+      </c>
+      <c r="J54">
+        <v>4</v>
+      </c>
+      <c r="K54">
+        <v>4</v>
+      </c>
+      <c r="L54" t="s">
         <v>158</v>
-      </c>
-      <c r="E54" t="s">
-        <v>147</v>
-      </c>
-      <c r="F54" t="s">
-        <v>18</v>
-      </c>
-      <c r="G54">
-        <v>4</v>
-      </c>
-      <c r="H54">
-        <v>4</v>
-      </c>
-      <c r="I54">
-        <v>4</v>
-      </c>
-      <c r="J54">
-        <v>4</v>
-      </c>
-      <c r="K54">
-        <v>4</v>
-      </c>
-      <c r="L54" t="s">
-        <v>159</v>
       </c>
       <c r="M54" t="s">
         <v>33</v>
@@ -3320,19 +3330,19 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" t="s">
+        <v>159</v>
+      </c>
+      <c r="B55" t="s">
+        <v>138</v>
+      </c>
+      <c r="C55" t="s">
         <v>160</v>
       </c>
-      <c r="B55" t="s">
-        <v>139</v>
-      </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>161</v>
       </c>
-      <c r="D55" t="s">
-        <v>162</v>
-      </c>
       <c r="E55" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F55" t="s">
         <v>18</v>
@@ -3353,7 +3363,7 @@
         <v>4</v>
       </c>
       <c r="L55" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M55" t="s">
         <v>20</v>
@@ -3361,40 +3371,40 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" t="s">
+        <v>162</v>
+      </c>
+      <c r="B56" t="s">
+        <v>138</v>
+      </c>
+      <c r="C56" t="s">
+        <v>160</v>
+      </c>
+      <c r="D56" t="s">
         <v>163</v>
       </c>
-      <c r="B56" t="s">
-        <v>139</v>
-      </c>
-      <c r="C56" t="s">
-        <v>161</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
+        <v>146</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56">
+        <v>5</v>
+      </c>
+      <c r="H56">
+        <v>5</v>
+      </c>
+      <c r="I56">
+        <v>4</v>
+      </c>
+      <c r="J56">
+        <v>5</v>
+      </c>
+      <c r="K56">
+        <v>4</v>
+      </c>
+      <c r="L56" t="s">
         <v>164</v>
-      </c>
-      <c r="E56" t="s">
-        <v>147</v>
-      </c>
-      <c r="F56" t="s">
-        <v>18</v>
-      </c>
-      <c r="G56">
-        <v>5</v>
-      </c>
-      <c r="H56">
-        <v>5</v>
-      </c>
-      <c r="I56">
-        <v>4</v>
-      </c>
-      <c r="J56">
-        <v>5</v>
-      </c>
-      <c r="K56">
-        <v>4</v>
-      </c>
-      <c r="L56" t="s">
-        <v>165</v>
       </c>
       <c r="M56" t="s">
         <v>20</v>
@@ -3402,19 +3412,19 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" t="s">
+        <v>165</v>
+      </c>
+      <c r="B57" t="s">
+        <v>138</v>
+      </c>
+      <c r="C57" t="s">
+        <v>160</v>
+      </c>
+      <c r="D57" t="s">
         <v>166</v>
       </c>
-      <c r="B57" t="s">
-        <v>139</v>
-      </c>
-      <c r="C57" t="s">
-        <v>161</v>
-      </c>
-      <c r="D57" t="s">
-        <v>167</v>
-      </c>
       <c r="E57" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F57" t="s">
         <v>18</v>
@@ -3435,7 +3445,7 @@
         <v>4</v>
       </c>
       <c r="L57" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M57" t="s">
         <v>33</v>
@@ -3443,40 +3453,40 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" t="s">
+        <v>167</v>
+      </c>
+      <c r="B58" t="s">
+        <v>138</v>
+      </c>
+      <c r="C58" t="s">
+        <v>115</v>
+      </c>
+      <c r="D58" t="s">
         <v>168</v>
       </c>
-      <c r="B58" t="s">
-        <v>139</v>
-      </c>
-      <c r="C58" t="s">
-        <v>116</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
+        <v>146</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58">
+        <v>4</v>
+      </c>
+      <c r="H58">
+        <v>4</v>
+      </c>
+      <c r="I58">
+        <v>4</v>
+      </c>
+      <c r="J58">
+        <v>4</v>
+      </c>
+      <c r="K58">
+        <v>4</v>
+      </c>
+      <c r="L58" t="s">
         <v>169</v>
-      </c>
-      <c r="E58" t="s">
-        <v>147</v>
-      </c>
-      <c r="F58" t="s">
-        <v>18</v>
-      </c>
-      <c r="G58">
-        <v>4</v>
-      </c>
-      <c r="H58">
-        <v>4</v>
-      </c>
-      <c r="I58">
-        <v>4</v>
-      </c>
-      <c r="J58">
-        <v>4</v>
-      </c>
-      <c r="K58">
-        <v>4</v>
-      </c>
-      <c r="L58" t="s">
-        <v>170</v>
       </c>
       <c r="M58" t="s">
         <v>33</v>
@@ -3484,40 +3494,40 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" t="s">
+        <v>170</v>
+      </c>
+      <c r="B59" t="s">
+        <v>138</v>
+      </c>
+      <c r="C59" t="s">
         <v>171</v>
       </c>
-      <c r="B59" t="s">
-        <v>139</v>
-      </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>172</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
+        <v>146</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59">
+        <v>4</v>
+      </c>
+      <c r="H59">
+        <v>4</v>
+      </c>
+      <c r="I59">
+        <v>4</v>
+      </c>
+      <c r="J59">
+        <v>4</v>
+      </c>
+      <c r="K59">
+        <v>4</v>
+      </c>
+      <c r="L59" t="s">
         <v>173</v>
-      </c>
-      <c r="E59" t="s">
-        <v>147</v>
-      </c>
-      <c r="F59" t="s">
-        <v>18</v>
-      </c>
-      <c r="G59">
-        <v>4</v>
-      </c>
-      <c r="H59">
-        <v>4</v>
-      </c>
-      <c r="I59">
-        <v>4</v>
-      </c>
-      <c r="J59">
-        <v>4</v>
-      </c>
-      <c r="K59">
-        <v>4</v>
-      </c>
-      <c r="L59" t="s">
-        <v>174</v>
       </c>
       <c r="M59" t="s">
         <v>33</v>
@@ -3525,40 +3535,40 @@
     </row>
     <row r="60" spans="1:13">
       <c r="A60" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B60" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C60" t="s">
         <v>76</v>
       </c>
       <c r="D60" t="s">
+        <v>175</v>
+      </c>
+      <c r="E60" t="s">
+        <v>146</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60">
+        <v>4</v>
+      </c>
+      <c r="H60">
+        <v>4</v>
+      </c>
+      <c r="I60">
+        <v>4</v>
+      </c>
+      <c r="J60">
+        <v>4</v>
+      </c>
+      <c r="K60">
+        <v>4</v>
+      </c>
+      <c r="L60" t="s">
         <v>176</v>
-      </c>
-      <c r="E60" t="s">
-        <v>147</v>
-      </c>
-      <c r="F60" t="s">
-        <v>18</v>
-      </c>
-      <c r="G60">
-        <v>4</v>
-      </c>
-      <c r="H60">
-        <v>4</v>
-      </c>
-      <c r="I60">
-        <v>4</v>
-      </c>
-      <c r="J60">
-        <v>4</v>
-      </c>
-      <c r="K60">
-        <v>4</v>
-      </c>
-      <c r="L60" t="s">
-        <v>177</v>
       </c>
       <c r="M60" t="s">
         <v>33</v>
@@ -3566,40 +3576,40 @@
     </row>
     <row r="61" spans="1:13">
       <c r="A61" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B61" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C61" t="s">
         <v>25</v>
       </c>
       <c r="D61" t="s">
+        <v>178</v>
+      </c>
+      <c r="E61" t="s">
+        <v>146</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61">
+        <v>4</v>
+      </c>
+      <c r="H61">
+        <v>4</v>
+      </c>
+      <c r="I61">
+        <v>4</v>
+      </c>
+      <c r="J61">
+        <v>4</v>
+      </c>
+      <c r="K61">
+        <v>4</v>
+      </c>
+      <c r="L61" t="s">
         <v>179</v>
-      </c>
-      <c r="E61" t="s">
-        <v>147</v>
-      </c>
-      <c r="F61" t="s">
-        <v>18</v>
-      </c>
-      <c r="G61">
-        <v>4</v>
-      </c>
-      <c r="H61">
-        <v>4</v>
-      </c>
-      <c r="I61">
-        <v>4</v>
-      </c>
-      <c r="J61">
-        <v>4</v>
-      </c>
-      <c r="K61">
-        <v>4</v>
-      </c>
-      <c r="L61" t="s">
-        <v>180</v>
       </c>
       <c r="M61" t="s">
         <v>33</v>
@@ -3607,40 +3617,40 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B62" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C62" t="s">
         <v>25</v>
       </c>
       <c r="D62" t="s">
+        <v>181</v>
+      </c>
+      <c r="E62" t="s">
+        <v>146</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62">
+        <v>4</v>
+      </c>
+      <c r="H62">
+        <v>4</v>
+      </c>
+      <c r="I62">
+        <v>4</v>
+      </c>
+      <c r="J62">
+        <v>4</v>
+      </c>
+      <c r="K62">
+        <v>4</v>
+      </c>
+      <c r="L62" t="s">
         <v>182</v>
-      </c>
-      <c r="E62" t="s">
-        <v>147</v>
-      </c>
-      <c r="F62" t="s">
-        <v>18</v>
-      </c>
-      <c r="G62">
-        <v>4</v>
-      </c>
-      <c r="H62">
-        <v>4</v>
-      </c>
-      <c r="I62">
-        <v>4</v>
-      </c>
-      <c r="J62">
-        <v>4</v>
-      </c>
-      <c r="K62">
-        <v>4</v>
-      </c>
-      <c r="L62" t="s">
-        <v>183</v>
       </c>
       <c r="M62" t="s">
         <v>33</v>
@@ -3648,19 +3658,19 @@
     </row>
     <row r="63" spans="1:13">
       <c r="A63" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B63" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C63" t="s">
         <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E63" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F63" t="s">
         <v>18</v>
@@ -3681,7 +3691,7 @@
         <v>4</v>
       </c>
       <c r="L63" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M63" t="s">
         <v>33</v>
@@ -3689,40 +3699,40 @@
     </row>
     <row r="64" spans="1:13">
       <c r="A64" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B64" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C64" t="s">
         <v>15</v>
       </c>
       <c r="D64" t="s">
+        <v>205</v>
+      </c>
+      <c r="E64" t="s">
+        <v>199</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64">
+        <v>3</v>
+      </c>
+      <c r="H64">
+        <v>5</v>
+      </c>
+      <c r="I64">
+        <v>4</v>
+      </c>
+      <c r="J64">
+        <v>4</v>
+      </c>
+      <c r="K64">
+        <v>4</v>
+      </c>
+      <c r="L64" t="s">
         <v>206</v>
-      </c>
-      <c r="E64" t="s">
-        <v>200</v>
-      </c>
-      <c r="F64" t="s">
-        <v>18</v>
-      </c>
-      <c r="G64">
-        <v>3</v>
-      </c>
-      <c r="H64">
-        <v>5</v>
-      </c>
-      <c r="I64">
-        <v>4</v>
-      </c>
-      <c r="J64">
-        <v>4</v>
-      </c>
-      <c r="K64">
-        <v>4</v>
-      </c>
-      <c r="L64" t="s">
-        <v>207</v>
       </c>
       <c r="M64" t="s">
         <v>45</v>
@@ -3730,19 +3740,19 @@
     </row>
     <row r="65" spans="1:13">
       <c r="A65" t="s">
+        <v>185</v>
+      </c>
+      <c r="B65" t="s">
+        <v>138</v>
+      </c>
+      <c r="C65" t="s">
+        <v>160</v>
+      </c>
+      <c r="D65" t="s">
         <v>186</v>
       </c>
-      <c r="B65" t="s">
-        <v>139</v>
-      </c>
-      <c r="C65" t="s">
-        <v>161</v>
-      </c>
-      <c r="D65" t="s">
-        <v>187</v>
-      </c>
       <c r="E65" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F65" t="s">
         <v>18</v>
@@ -3763,7 +3773,7 @@
         <v>4</v>
       </c>
       <c r="L65" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M65" t="s">
         <v>45</v>
